--- a/prix/plasson.xlsx
+++ b/prix/plasson.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8A4801-B8B8-4501-A1D0-88BA96DB242A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4600A375-3F30-4F7E-B578-A0BABBF91580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2B4B34BF-6B13-4E9C-8318-8F04E76BBCB4}"/>
   </bookViews>
@@ -220,14 +220,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,7 +595,7 @@
       <c r="E1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G1" s="1"/>
@@ -617,13 +617,13 @@
       <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="10">
         <v>11.35</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>5</v>
       </c>
     </row>
@@ -637,13 +637,13 @@
       <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="10">
         <v>14.21</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>5</v>
       </c>
     </row>
@@ -657,13 +657,13 @@
       <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="10">
         <v>11.35</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>0</v>
       </c>
     </row>
@@ -677,13 +677,13 @@
       <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="10">
         <v>11.35</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>0</v>
       </c>
     </row>
@@ -697,13 +697,13 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="10">
         <v>7.13</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>12</v>
       </c>
     </row>
@@ -717,13 +717,13 @@
       <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="10">
         <v>9.0400000000000009</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>5</v>
       </c>
     </row>
@@ -737,13 +737,13 @@
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="10">
         <v>7.34</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>7</v>
       </c>
     </row>
@@ -757,13 +757,13 @@
       <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="10">
         <v>9.15</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>8</v>
       </c>
     </row>
@@ -777,13 +777,13 @@
       <c r="C10" s="6">
         <v>25</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="10">
         <v>16.64</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>2</v>
       </c>
     </row>
@@ -797,13 +797,13 @@
       <c r="C11" s="6">
         <v>32</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="10">
         <v>21.91</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>0</v>
       </c>
     </row>

--- a/prix/plasson.xlsx
+++ b/prix/plasson.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4600A375-3F30-4F7E-B578-A0BABBF91580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8B6725-2BE7-4470-891F-D78457F94E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2B4B34BF-6B13-4E9C-8318-8F04E76BBCB4}"/>
   </bookViews>
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -222,12 +222,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -617,13 +611,13 @@
       <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="2">
         <v>11.35</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="3">
         <v>5</v>
       </c>
     </row>
@@ -637,13 +631,13 @@
       <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="2">
         <v>14.21</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="3">
         <v>5</v>
       </c>
     </row>
@@ -657,13 +651,13 @@
       <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="2">
         <v>11.35</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="3">
         <v>0</v>
       </c>
     </row>
@@ -677,13 +671,13 @@
       <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="2">
         <v>11.35</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="3">
         <v>0</v>
       </c>
     </row>
@@ -697,13 +691,13 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="2">
         <v>7.13</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="3">
         <v>12</v>
       </c>
     </row>
@@ -717,13 +711,13 @@
       <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="2">
         <v>9.0400000000000009</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="3">
         <v>5</v>
       </c>
     </row>
@@ -737,13 +731,13 @@
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="2">
         <v>7.34</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="3">
         <v>7</v>
       </c>
     </row>
@@ -757,13 +751,13 @@
       <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="2">
         <v>9.15</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="3">
         <v>8</v>
       </c>
     </row>
@@ -777,13 +771,13 @@
       <c r="C10" s="6">
         <v>25</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="2">
         <v>16.64</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="3">
         <v>2</v>
       </c>
     </row>
@@ -797,13 +791,13 @@
       <c r="C11" s="6">
         <v>32</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="2">
         <v>21.91</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="3">
         <v>0</v>
       </c>
     </row>

--- a/prix/plasson.xlsx
+++ b/prix/plasson.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8B6725-2BE7-4470-891F-D78457F94E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04550974-3802-4C29-96A5-3B15BA03749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2B4B34BF-6B13-4E9C-8318-8F04E76BBCB4}"/>
+    <workbookView xWindow="23124" yWindow="480" windowWidth="19116" windowHeight="10884" xr2:uid="{2B4B34BF-6B13-4E9C-8318-8F04E76BBCB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -222,6 +222,12 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,13 +617,13 @@
       <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="9">
         <v>11.35</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="10">
         <v>5</v>
       </c>
     </row>
@@ -631,14 +637,14 @@
       <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="9">
         <v>14.21</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3">
-        <v>5</v>
+      <c r="F3" s="10">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -651,13 +657,13 @@
       <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="9">
         <v>11.35</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="10">
         <v>0</v>
       </c>
     </row>
@@ -671,13 +677,13 @@
       <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="9">
         <v>11.35</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="10">
         <v>0</v>
       </c>
     </row>
@@ -691,13 +697,13 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="9">
         <v>7.13</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="10">
         <v>12</v>
       </c>
     </row>
@@ -711,14 +717,14 @@
       <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <v>9.0400000000000009</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="3">
-        <v>5</v>
+      <c r="F7" s="10">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -731,13 +737,13 @@
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="9">
         <v>7.34</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="10">
         <v>7</v>
       </c>
     </row>
@@ -751,13 +757,13 @@
       <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="9">
         <v>9.15</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="10">
         <v>8</v>
       </c>
     </row>
@@ -771,13 +777,13 @@
       <c r="C10" s="6">
         <v>25</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="9">
         <v>16.64</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="10">
         <v>2</v>
       </c>
     </row>
@@ -791,13 +797,13 @@
       <c r="C11" s="6">
         <v>32</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="9">
         <v>21.91</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="10">
         <v>0</v>
       </c>
     </row>

--- a/prix/plasson.xlsx
+++ b/prix/plasson.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04550974-3802-4C29-96A5-3B15BA03749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C635BD53-D773-486F-9558-21229A4E86B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23124" yWindow="480" windowWidth="19116" windowHeight="10884" xr2:uid="{2B4B34BF-6B13-4E9C-8318-8F04E76BBCB4}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2B4B34BF-6B13-4E9C-8318-8F04E76BBCB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -222,6 +222,12 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -657,13 +663,13 @@
       <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="11">
         <v>11.35</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="12">
         <v>0</v>
       </c>
     </row>
@@ -677,13 +683,13 @@
       <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="11">
         <v>11.35</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="12">
         <v>0</v>
       </c>
     </row>
@@ -697,13 +703,13 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="11">
         <v>7.13</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="12">
         <v>12</v>
       </c>
     </row>
@@ -717,13 +723,13 @@
       <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="11">
         <v>9.0400000000000009</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="12">
         <v>4</v>
       </c>
     </row>
@@ -737,13 +743,13 @@
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="11">
         <v>7.34</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="12">
         <v>7</v>
       </c>
     </row>
@@ -757,13 +763,13 @@
       <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="11">
         <v>9.15</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="12">
         <v>8</v>
       </c>
     </row>
@@ -777,13 +783,13 @@
       <c r="C10" s="6">
         <v>25</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="11">
         <v>16.64</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="12">
         <v>2</v>
       </c>
     </row>
@@ -797,13 +803,13 @@
       <c r="C11" s="6">
         <v>32</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="11">
         <v>21.91</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="12">
         <v>0</v>
       </c>
     </row>

--- a/prix/plasson.xlsx
+++ b/prix/plasson.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C635BD53-D773-486F-9558-21229A4E86B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC2C4D3-02EF-4DB9-A018-4F527FA68150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{2B4B34BF-6B13-4E9C-8318-8F04E76BBCB4}"/>
   </bookViews>
@@ -199,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -222,12 +222,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -663,13 +657,13 @@
       <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9">
         <v>11.35</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>0</v>
       </c>
     </row>
@@ -683,13 +677,13 @@
       <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="9">
         <v>11.35</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>0</v>
       </c>
     </row>
@@ -703,13 +697,13 @@
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <v>7.13</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>12</v>
       </c>
     </row>
@@ -723,13 +717,13 @@
       <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <v>9.0400000000000009</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>4</v>
       </c>
     </row>
@@ -743,13 +737,13 @@
       <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <v>7.34</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <v>7</v>
       </c>
     </row>
@@ -763,13 +757,13 @@
       <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="9">
         <v>9.15</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="10">
         <v>8</v>
       </c>
     </row>
@@ -783,13 +777,13 @@
       <c r="C10" s="6">
         <v>25</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>16.64</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="10">
         <v>2</v>
       </c>
     </row>
@@ -803,13 +797,13 @@
       <c r="C11" s="6">
         <v>32</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <v>21.91</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="10">
         <v>0</v>
       </c>
     </row>
